--- a/output/pdf_financials_xlsx/GRUN.xlsx
+++ b/output/pdf_financials_xlsx/GRUN.xlsx
@@ -715,16 +715,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.852608</v>
+        <v>-0.852608</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.853128</v>
+        <v>-0.853128</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.119635</v>
+        <v>-1.119635</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.260837</v>
+        <v>-0.260837</v>
       </c>
     </row>
     <row r="17">
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.852608</v>
+        <v>-0.852608</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.853128</v>
+        <v>-0.853128</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.119635</v>
+        <v>-1.119635</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.260837</v>
+        <v>-0.260837</v>
       </c>
     </row>
     <row r="21">
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.852608</v>
+        <v>-0.852608</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.853128</v>
+        <v>-0.853128</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.119635</v>
+        <v>-1.119635</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.260837</v>
+        <v>-0.260837</v>
       </c>
     </row>
     <row r="24">
@@ -921,16 +921,16 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>21.3152</v>
+        <v>-21.3152</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>28.4376</v>
+        <v>-28.4376</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>3.445031</v>
+        <v>-3.445031</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>3.835838</v>
+        <v>-3.835838</v>
       </c>
     </row>
     <row r="27">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.852608</v>
+        <v>-0.852608</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.853128</v>
+        <v>-0.853128</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.119635</v>
+        <v>-1.119635</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.260837</v>
+        <v>-0.260837</v>
       </c>
     </row>
     <row r="28">
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.852608</v>
+        <v>-0.852608</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.853128</v>
+        <v>-0.853128</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.119635</v>
+        <v>-1.119635</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.260837</v>
+        <v>-0.260837</v>
       </c>
     </row>
     <row r="30">
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2681,16 +2681,16 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.393042</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.308789</v>
+        <v>0.117276</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.715754</v>
+        <v>-0.161423</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.176246</v>
       </c>
     </row>
     <row r="119">
@@ -4670,7 +4670,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="n">
         <v>-0.393042</v>
       </c>
@@ -6682,10 +6686,10 @@
         </is>
       </c>
       <c r="G103" s="5" t="n">
-        <v>1.119635</v>
+        <v>-1.119635</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>0.260837</v>
+        <v>-0.260837</v>
       </c>
     </row>
     <row r="104">
@@ -7071,10 +7075,10 @@
         </is>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.853128</v>
+        <v>-0.853128</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>1.119635</v>
+        <v>-1.119635</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -7428,10 +7432,10 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.852608</v>
+        <v>-0.852608</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>0.853128</v>
+        <v>-0.853128</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GRUN.xlsx
+++ b/output/pdf_financials_xlsx/GRUN.xlsx
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.160188</v>
+        <v>0.253938</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.170023</v>
+        <v>0.252523</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.089127</v>
+        <v>0.154702</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.107599</v>
+        <v>0.150499</v>
       </c>
     </row>
     <row r="8">
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.160188</v>
+        <v>0.253938</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.170023</v>
+        <v>0.252523</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.089127</v>
+        <v>0.154702</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.107599</v>
+        <v>0.150499</v>
       </c>
     </row>
     <row r="11">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.160188</v>
+        <v>-0.253938</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>0.533926</v>
@@ -6188,7 +6188,11 @@
           <t>Director fees (Note 12)</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -6818,7 +6822,11 @@
           <t>Director fees (Note 11)</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -7216,7 +7224,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E118" s="5" t="n">
         <v>0.09375</v>
       </c>
